--- a/product_selector_out/STM32H523-533 - diff.xlsx
+++ b/product_selector_out/STM32H523-533 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$127</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -47,16 +47,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
@@ -68,6 +58,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEB9C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>872</v>
+        <v>863</v>
       </c>
     </row>
     <row r="18">
@@ -679,22 +679,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -706,10 +706,14 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>10</t>
@@ -717,7 +721,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -729,25 +733,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -762,10 +770,10 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E22" s="3" t="inlineStr">
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -774,54 +782,46 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E23" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -833,22 +833,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E25" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -887,22 +887,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E27" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E28" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -941,18 +941,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -964,70 +968,74 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E31" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="inlineStr">
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1036,25 +1044,25 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E33" s="6" t="inlineStr">
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1063,25 +1071,25 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E34" s="7" t="inlineStr">
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1090,54 +1098,46 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E36" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1149,22 +1149,22 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E37" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E37" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1176,10 +1176,14 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
           <t>10</t>
@@ -1187,7 +1191,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1199,25 +1203,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1232,10 +1240,10 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E40" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -1244,7 +1252,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1262,7 +1270,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E41" s="3" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1271,7 +1279,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1289,7 +1297,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr">
+      <c r="E42" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1298,7 +1306,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1316,7 +1324,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E43" s="7" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1325,7 +1333,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1343,7 +1351,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1352,7 +1360,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1370,7 +1378,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr">
+      <c r="E45" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1379,7 +1387,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1397,7 +1405,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E46" s="7" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1406,7 +1414,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -1420,7 +1428,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
+      <c r="E47" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1429,7 +1437,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1443,7 +1451,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
+      <c r="E48" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1452,107 +1460,115 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E51" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E52" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -1567,19 +1583,19 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E53" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E53" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1589,51 +1605,51 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -1648,19 +1664,19 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E56" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -1670,61 +1686,65 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E57" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1733,21 +1753,21 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="4" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1756,21 +1776,21 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E61" s="4" t="inlineStr">
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1779,21 +1799,21 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E62" s="4" t="inlineStr">
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -1802,38 +1822,46 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E63" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>10</t>
@@ -1841,37 +1869,41 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E65" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -1886,10 +1918,10 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E66" s="3" t="inlineStr">
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E66" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -1898,7 +1930,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -1913,10 +1945,10 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E67" s="5" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E67" s="3" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -1925,7 +1957,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -1940,10 +1972,10 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E68" s="6" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -1952,7 +1984,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -1967,10 +1999,10 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E69" s="7" t="inlineStr">
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -1979,7 +2011,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -1994,19 +2026,19 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -2021,10 +2053,10 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E71" s="6" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -2033,7 +2065,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2048,10 +2080,10 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E72" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -2060,7 +2092,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2074,7 +2106,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
+      <c r="E73" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2083,7 +2115,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2097,7 +2129,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
+      <c r="E74" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2106,204 +2138,184 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E76" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E77" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E79" s="5" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E79" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E80" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E81" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>10</t>
@@ -2311,37 +2323,41 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -2356,10 +2372,10 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E84" s="3" t="inlineStr">
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E84" s="6" t="inlineStr">
         <is>
           <t>BLANK_FILLED</t>
         </is>
@@ -2368,7 +2384,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -2386,7 +2402,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E85" s="3" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -2395,7 +2411,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -2413,7 +2429,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E86" s="6" t="inlineStr">
+      <c r="E86" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -2422,7 +2438,7 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -2440,7 +2456,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E87" s="7" t="inlineStr">
+      <c r="E87" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -2449,7 +2465,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -2467,7 +2483,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E88" s="5" t="inlineStr">
+      <c r="E88" s="3" t="inlineStr">
         <is>
           <t>CHANGED</t>
         </is>
@@ -2476,7 +2492,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -2494,7 +2510,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E89" s="6" t="inlineStr">
+      <c r="E89" s="4" t="inlineStr">
         <is>
           <t>DATASHEET_OVERRIDES_API</t>
         </is>
@@ -2503,7 +2519,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -2521,7 +2537,7 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E90" s="7" t="inlineStr">
+      <c r="E90" s="5" t="inlineStr">
         <is>
           <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
@@ -2530,7 +2546,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -2544,7 +2560,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
+      <c r="E91" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2553,7 +2569,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2567,7 +2583,7 @@
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
+      <c r="E92" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
@@ -2576,205 +2592,918 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>BLANK_FILLED</t>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="6" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E95" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="7" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E96" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E97" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>ADDED_COLUMN</t>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E99" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E100" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E101" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E102" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr"/>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>STM32H523VC</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr"/>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E108" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E110" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E111" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E112" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E113" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E121" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E122" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr"/>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>STM32H533ZE</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr"/>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr"/>
-      <c r="D100" t="inlineStr">
+      <c r="C127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
+      <c r="E127" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E100"/>
+  <autoFilter ref="A18:E127"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32H523-533 - diff.xlsx
+++ b/product_selector_out/STM32H523-533 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$154</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E127"/>
+  <dimension ref="A1:E154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9">
@@ -621,7 +621,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>863</v>
+        <v>854</v>
       </c>
     </row>
     <row r="18">
@@ -787,18 +787,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -810,99 +814,95 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E25" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -914,22 +914,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E28" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -941,22 +941,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E29" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -968,22 +968,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -995,22 +995,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1022,17 +1022,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
@@ -1049,17 +1049,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -1076,17 +1076,17 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -1103,18 +1103,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E35" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1126,180 +1130,176 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E36" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E37" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E38" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E39" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E41" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E43" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1338,22 +1338,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1365,22 +1365,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1392,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E46" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1419,18 +1419,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E47" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E47" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1442,148 +1446,152 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E48" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E48" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E50" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E52" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
@@ -1595,22 +1603,22 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
@@ -1622,22 +1630,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
@@ -1649,54 +1657,46 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E56" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1708,22 +1708,22 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E58" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1735,18 +1735,22 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E59" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1758,189 +1762,201 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E60" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E61" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E62" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E63" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E63" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E65" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E66" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -1948,70 +1964,70 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E67" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2021,78 +2037,70 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E70" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
       <c r="D72" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2115,7 +2123,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -2138,295 +2146,319 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E75" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E76" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E77" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E78" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E79" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E80" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E83" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E84" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E84" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E85" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E85" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
@@ -2438,22 +2470,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
@@ -2465,99 +2497,87 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E88" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>SD/MMC (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>Longevity Starting Date</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
@@ -2569,18 +2589,18 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
@@ -2592,211 +2612,199 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E93" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E95" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E96" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E97" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E98" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E99" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E100" s="3" t="inlineStr">
@@ -2808,22 +2816,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
@@ -2835,22 +2843,22 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
@@ -2862,477 +2870,485 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E103" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E103" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E104" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E104" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E105" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E105" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E107" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E107" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E108" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr"/>
       <c r="D109" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E109" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E111" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E111" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E112" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E114" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E114" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E115" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E115" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E116" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E116" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E117" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E119" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E120" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3347,19 +3363,19 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E121" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3374,7 +3390,7 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -3386,7 +3402,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3401,7 +3417,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -3413,7 +3429,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3436,7 +3452,7 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3459,51 +3475,764 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="D126" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E126" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E126" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E127" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E129" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E130" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E131" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E133" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E134" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E136" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E137" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr"/>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E139" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>STM32H523RC</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E140" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E141" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E142" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E144" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E145" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E146" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E148" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E149" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E151" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E152" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
           <t>STM32H533ZE</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E153" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr"/>
-      <c r="D127" t="inlineStr">
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E127" s="7" t="inlineStr">
+      <c r="E154" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E127"/>
+  <autoFilter ref="A18:E154"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/product_selector_out/STM32H523-533 - diff.xlsx
+++ b/product_selector_out/STM32H523-533 - diff.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Diff" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$154</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Diff'!$A$18:$E$163</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -468,7 +468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E154"/>
+  <dimension ref="A1:E163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>924</v>
+        <v>938</v>
       </c>
     </row>
     <row r="6">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -591,7 +591,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
     </row>
     <row r="12">
@@ -641,7 +641,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>854</v>
+        <v>859</v>
       </c>
     </row>
     <row r="18">
@@ -909,27 +909,23 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>STM32H523ZE</t>
+          <t>STM32H523CE</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -954,9 +950,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -973,7 +969,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -981,9 +977,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -995,22 +991,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E31" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1022,22 +1018,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E32" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E32" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1062,9 +1058,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1081,7 +1077,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1089,9 +1085,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1103,22 +1099,22 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1143,9 +1139,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1162,7 +1158,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1170,9 +1166,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1184,22 +1180,22 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1224,9 +1220,9 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1243,7 +1239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1251,9 +1247,9 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1265,18 +1261,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E41" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1288,13 +1288,13 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
@@ -1306,54 +1306,46 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E43" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>STM32H523RE</t>
+          <t>STM32H523ZE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1362,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1378,9 +1370,9 @@
           <t>10</t>
         </is>
       </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E45" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1392,22 +1384,22 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E46" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1419,22 +1411,22 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E47" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1446,22 +1438,22 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E48" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1478,7 +1470,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1486,9 +1478,9 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E49" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1500,22 +1492,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E50" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1519,22 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1551,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1567,9 +1559,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E52" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1581,22 +1573,22 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E53" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1608,22 +1600,22 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1640,7 +1632,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1648,9 +1640,9 @@
           <t>Parallel camera interface</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E55" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1662,18 +1654,22 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1685,99 +1681,91 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E58" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>STM32H523VE</t>
+          <t>STM32H523RE</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -1789,22 +1777,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E61" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E61" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -1816,22 +1804,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E62" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E62" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -1843,22 +1831,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -1870,22 +1858,22 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E64" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E64" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -1897,17 +1885,17 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
@@ -1924,17 +1912,17 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
@@ -1951,17 +1939,17 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
@@ -1978,17 +1966,17 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E68" s="3" t="inlineStr">
@@ -2005,17 +1993,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
@@ -2032,17 +2020,17 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
@@ -2059,18 +2047,22 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E71" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E71" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2082,59 +2074,67 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E73" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>STM32H533VE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
@@ -2146,108 +2146,92 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
       <c r="D75" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E75" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H523VE</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E77" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>STM32H523HE</t>
+          <t>STM32H533VE</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" t="inlineStr">
         <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E78" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2259,17 +2243,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
@@ -2286,17 +2270,17 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
@@ -2313,17 +2297,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
@@ -2340,22 +2324,22 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E82" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E82" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2351,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2380,9 +2364,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E83" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2394,12 +2378,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2407,9 +2391,9 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+      <c r="E84" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2421,22 +2405,22 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2448,22 +2432,22 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2475,22 +2459,22 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E87" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2502,18 +2486,22 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E88" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2525,71 +2513,83 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E89" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E90" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>STM32H533CE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -2612,7 +2612,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>STM32H533RE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -2635,18 +2635,18 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H523HE</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
+          <t>LPUART typ</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
@@ -2658,18 +2658,18 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>STM32H533HE</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
+          <t>Longevity Commitment (yr) typ</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
@@ -2681,135 +2681,115 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533CE</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr"/>
       <c r="D96" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
       <c r="D97" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533RE</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>5 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
       <c r="D98" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E98" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
       <c r="D99" t="inlineStr">
         <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="E99" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>STM32H523ZC</t>
+          <t>STM32H533HE</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -2821,22 +2801,22 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E101" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2848,22 +2828,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E102" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E102" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2875,22 +2855,22 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E103" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -2902,22 +2882,22 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="E104" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -2929,22 +2909,22 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E105" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E105" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -2956,22 +2936,22 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E106" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -2983,22 +2963,22 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E107" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3010,22 +2990,22 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E108" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3037,18 +3017,22 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E109" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E109" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3060,40 +3044,44 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E110" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
@@ -3105,22 +3093,22 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
@@ -3132,22 +3120,22 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>Parallel camera interface</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
@@ -3159,81 +3147,69 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr"/>
       <c r="D114" t="inlineStr">
         <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="E114" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E115" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>STM32H523VC</t>
+          <t>STM32H523ZC</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3245,22 +3221,22 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>USART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3 (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E117" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3272,22 +3248,22 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E118" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E118" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3299,22 +3275,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3326,22 +3302,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E120" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3353,17 +3329,17 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
@@ -3380,17 +3356,17 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
@@ -3407,17 +3383,17 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -3434,18 +3410,22 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E124" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3457,207 +3437,199 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E125" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E125" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E126" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E128" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="E129" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr"/>
       <c r="D130" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E130" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>STM32H523RC</t>
+          <t>STM32H523VC</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>USART typ</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>3 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr"/>
       <c r="D132" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E132" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -3669,17 +3641,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
@@ -3696,17 +3668,17 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
@@ -3723,17 +3695,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>4 (workbook and API agree)</t>
+          <t>5 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr">
@@ -3750,22 +3722,22 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>I/Os (High Current)</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="E136" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
@@ -3777,22 +3749,22 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E137" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -3804,22 +3776,22 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>USART typ</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Parallel camera interface</t>
-        </is>
-      </c>
-      <c r="E138" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E138" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -3831,18 +3803,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr"/>
+          <t>USART typ</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>3 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E139" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -3854,234 +3830,226 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E140" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E140" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E141" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E141" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>UART typ</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4 (workbook and API agree)</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>5 (workbook and API agree)</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E143" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>I/Os (High Current)</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>SD/MMC</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>35</t>
-        </is>
-      </c>
-      <c r="E144" s="6" t="inlineStr">
-        <is>
-          <t>BLANK_FILLED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>UART typ</t>
+          <t>Additional Interfaces</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>SD/MMC (workbook and API agree)</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E145" s="3" t="inlineStr">
-        <is>
-          <t>CHANGED</t>
+          <t>Parallel camera interface</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr"/>
       <c r="D146" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E146" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>UART typ</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>4 (workbook and API agree)</t>
-        </is>
-      </c>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E147" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>STM32H523CC</t>
+          <t>STM32H523RC</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>SD/MMC</t>
-        </is>
-      </c>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E148" s="8" t="inlineStr">
-        <is>
-          <t>MISSING_FROM_ST</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E148" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
@@ -4093,22 +4061,22 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>SD/MMC</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>DATASHEET_OVERRIDES_API</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E149" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
@@ -4120,22 +4088,22 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Additional Interfaces</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>SD/MMC (workbook and API agree)</t>
+          <t>5</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="inlineStr">
-        <is>
-          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E150" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
         </is>
       </c>
     </row>
@@ -4147,18 +4115,22 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>Timers (16-bit) typ</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>5 (workbook and API agree)</t>
+        </is>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="E151" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+      <c r="E151" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
         </is>
       </c>
     </row>
@@ -4170,69 +4142,304 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Longevity Starting Date</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr"/>
+          <t>I/Os (High Current)</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>2026-01-01T00:00:00.000+01:00</t>
-        </is>
-      </c>
-      <c r="E152" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="E152" s="6" t="inlineStr">
+        <is>
+          <t>BLANK_FILLED</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>STM32H533ZE</t>
+          <t>STM32H523CC</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Longevity Commitment (yr) typ</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr"/>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="E153" s="7" t="inlineStr">
-        <is>
-          <t>ADDED_COLUMN</t>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="inlineStr">
+        <is>
+          <t>CHANGED</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E154" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>UART typ</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>4 (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E155" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E156" s="8" t="inlineStr">
+        <is>
+          <t>MISSING_FROM_ST</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>SD/MMC</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E157" s="4" t="inlineStr">
+        <is>
+          <t>DATASHEET_OVERRIDES_API</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Additional Interfaces</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>SD/MMC (workbook and API agree)</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E158" s="5" t="inlineStr">
+        <is>
+          <t>ORIGINAL_MATCHED_API_NOT_DATASHEET</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E159" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Longevity Starting Date</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>2026-01-01T00:00:00.000+01:00</t>
+        </is>
+      </c>
+      <c r="E160" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>STM32H523CC</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E161" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
           <t>STM32H533ZE</t>
         </is>
       </c>
-      <c r="B154" t="inlineStr">
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Longevity Commitment (yr) typ</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E162" s="7" t="inlineStr">
+        <is>
+          <t>ADDED_COLUMN</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>STM32H533ZE</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
         <is>
           <t>Longevity Starting Date</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
-      <c r="D154" t="inlineStr">
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr">
         <is>
           <t>2026-01-01T00:00:00.000+01:00</t>
         </is>
       </c>
-      <c r="E154" s="7" t="inlineStr">
+      <c r="E163" s="7" t="inlineStr">
         <is>
           <t>ADDED_COLUMN</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A18:E154"/>
+  <autoFilter ref="A18:E163"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>